--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Segnalazioni, suggerimenti e reclami.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Segnalazioni, suggerimenti e reclami.xlsx
@@ -447,7 +447,7 @@
     </r>
   </si>
   <si>
-    <t>Visualizza la tua segnalazione</t>
+    <t>Vai alla tua segnalazione</t>
   </si>
   <si>
     <t>-</t>
@@ -470,7 +470,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
